--- a/www/flightdata/xlsx/eoss-386.xlsx
+++ b/www/flightdata/xlsx/eoss-386.xlsx
@@ -2925,7 +2925,7 @@
         <v>30445.86</v>
       </c>
       <c r="I2">
-        <v>543</v>
+        <v>350</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
